--- a/Team-Data/2011-12/4-15-2011-12.xlsx
+++ b/Team-Data/2011-12/4-15-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,43 +728,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
         <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.583</v>
+        <v>0.593</v>
       </c>
       <c r="H2" t="n">
         <v>49.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J2" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K2" t="n">
         <v>0.449</v>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M2" t="n">
         <v>19.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O2" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0.738</v>
@@ -709,7 +776,7 @@
         <v>31.2</v>
       </c>
       <c r="T2" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U2" t="n">
         <v>22.1</v>
@@ -718,10 +785,10 @@
         <v>13.9</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y2" t="n">
         <v>4.9</v>
@@ -733,28 +800,28 @@
         <v>19.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
@@ -763,7 +830,7 @@
         <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM2" t="n">
         <v>13</v>
@@ -772,10 +839,10 @@
         <v>5</v>
       </c>
       <c r="AO2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP2" t="n">
         <v>24</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
@@ -784,19 +851,19 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
@@ -814,7 +881,7 @@
         <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -861,82 +928,82 @@
         <v>35.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.459</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P3" t="n">
         <v>19.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R3" t="n">
         <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T3" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="U3" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB3" t="n">
         <v>91.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,10 +1018,10 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
         <v>28</v>
@@ -966,22 +1033,22 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>28</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -990,13 +1057,13 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1046,7 +1113,7 @@
         <v>80.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.418</v>
+        <v>0.419</v>
       </c>
       <c r="L4" t="n">
         <v>4.1</v>
@@ -1055,7 +1122,7 @@
         <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
@@ -1088,22 +1155,22 @@
         <v>5.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="AC4" t="n">
         <v>-13.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1154,25 +1221,25 @@
         <v>30</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ4" t="n">
         <v>11</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,7 +1292,7 @@
         <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K5" t="n">
         <v>0.452</v>
@@ -1237,7 +1304,7 @@
         <v>16.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
         <v>15.5</v>
@@ -1255,13 +1322,13 @@
         <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="U5" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.1</v>
@@ -1276,16 +1343,16 @@
         <v>17.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC5" t="n">
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1318,7 +1385,7 @@
         <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
         <v>19</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L6" t="n">
         <v>6.8</v>
@@ -1419,37 +1486,37 @@
         <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T6" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
@@ -1461,13 +1528,13 @@
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.1</v>
+        <v>-5.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1479,10 +1546,10 @@
         <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
@@ -1491,10 +1558,10 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN6" t="n">
         <v>13</v>
@@ -1512,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1527,7 +1594,7 @@
         <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J7" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L7" t="n">
         <v>7.5</v>
@@ -1601,37 +1668,37 @@
         <v>22.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.339</v>
+        <v>0.336</v>
       </c>
       <c r="O7" t="n">
         <v>15.1</v>
       </c>
       <c r="P7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S7" t="n">
         <v>32.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
         <v>21.1</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
@@ -1643,16 +1710,16 @@
         <v>18.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1661,13 +1728,13 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
         <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK7" t="n">
         <v>19</v>
@@ -1688,7 +1755,7 @@
         <v>27</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>27</v>
@@ -1700,10 +1767,10 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1721,10 +1788,10 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.55</v>
+        <v>0.542</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1774,22 +1841,22 @@
         <v>81.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O8" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0.735</v>
@@ -1798,19 +1865,19 @@
         <v>11.3</v>
       </c>
       <c r="S8" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T8" t="n">
         <v>43.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>5.1</v>
@@ -1819,25 +1886,25 @@
         <v>6.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB8" t="n">
         <v>103.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -1879,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1888,7 +1955,7 @@
         <v>27</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>15</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="H9" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I9" t="n">
         <v>34.6</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,16 +2032,16 @@
         <v>13.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R9" t="n">
         <v>11.8</v>
@@ -1986,16 +2053,16 @@
         <v>39.9</v>
       </c>
       <c r="U9" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
         <v>5.4</v>
@@ -2004,28 +2071,28 @@
         <v>19.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="AC9" t="n">
         <v>-5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
@@ -2034,7 +2101,7 @@
         <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2073,13 +2140,13 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2207,10 +2274,10 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>12</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2252,10 +2319,10 @@
         <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
@@ -2267,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -2299,34 +2366,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.533</v>
+        <v>0.542</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J11" t="n">
         <v>83.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
         <v>0.36</v>
@@ -2338,7 +2405,7 @@
         <v>20</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.788</v>
+        <v>0.791</v>
       </c>
       <c r="R11" t="n">
         <v>11.6</v>
@@ -2350,43 +2417,43 @@
         <v>42</v>
       </c>
       <c r="U11" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y11" t="n">
         <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>4</v>
@@ -2404,13 +2471,13 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN11" t="n">
         <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>18</v>
@@ -2431,7 +2498,7 @@
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
@@ -2446,13 +2513,13 @@
         <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -2559,28 +2626,28 @@
         <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
         <v>21</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2589,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2604,7 +2671,7 @@
         <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -2613,7 +2680,7 @@
         <v>30</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
@@ -2631,10 +2698,10 @@
         <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
@@ -2774,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -2792,7 +2859,7 @@
         <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>2</v>
@@ -2801,10 +2868,10 @@
         <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
@@ -2816,7 +2883,7 @@
         <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.639</v>
+        <v>0.633</v>
       </c>
       <c r="H14" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I14" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J14" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.458</v>
@@ -2875,7 +2942,7 @@
         <v>17.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.325</v>
+        <v>0.324</v>
       </c>
       <c r="O14" t="n">
         <v>18.2</v>
@@ -2899,13 +2966,13 @@
         <v>22.1</v>
       </c>
       <c r="V14" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W14" t="n">
         <v>5.8</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
@@ -2917,13 +2984,13 @@
         <v>20.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2938,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="AI14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2974,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
         <v>22</v>
@@ -2983,7 +3050,7 @@
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>5</v>
@@ -2995,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -3027,40 +3094,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
         <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.583</v>
+        <v>0.593</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L15" t="n">
         <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O15" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
         <v>23.2</v>
@@ -3081,10 +3148,10 @@
         <v>19.6</v>
       </c>
       <c r="V15" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W15" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X15" t="n">
         <v>5.1</v>
@@ -3093,40 +3160,40 @@
         <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3144,19 +3211,19 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
@@ -3165,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>22</v>
@@ -3174,10 +3241,10 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.712</v>
+        <v>0.707</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J16" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K16" t="n">
         <v>0.474</v>
@@ -3236,31 +3303,31 @@
         <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O16" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P16" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T16" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V16" t="n">
         <v>14.8</v>
@@ -3269,28 +3336,28 @@
         <v>9.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z16" t="n">
         <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="AC16" t="n">
         <v>6.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3302,7 +3369,7 @@
         <v>3</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3317,7 +3384,7 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3326,22 +3393,22 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3490,25 +3557,25 @@
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
         <v>17</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR17" t="n">
         <v>6</v>
@@ -3544,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3690,7 +3757,7 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3702,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3906,7 @@
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
         <v>24</v>
@@ -3860,13 +3927,13 @@
         <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN19" t="n">
         <v>17</v>
       </c>
       <c r="AO19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP19" t="n">
         <v>15</v>
@@ -3887,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3</v>
+        <v>0.288</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,37 +4022,37 @@
         <v>35.2</v>
       </c>
       <c r="J20" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.452</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M20" t="n">
         <v>11.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O20" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P20" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.76</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S20" t="n">
         <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U20" t="n">
         <v>20.9</v>
@@ -3994,28 +4061,28 @@
         <v>15.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB20" t="n">
         <v>89.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.9</v>
+        <v>-4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4045,7 +4112,7 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -4054,13 +4121,13 @@
         <v>25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4072,13 +4139,13 @@
         <v>25</v>
       </c>
       <c r="AW20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX20" t="n">
         <v>20</v>
       </c>
-      <c r="AX20" t="n">
-        <v>21</v>
-      </c>
       <c r="AY20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
         <v>31</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.517</v>
+        <v>0.525</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J21" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K21" t="n">
         <v>0.439</v>
@@ -4146,28 +4213,28 @@
         <v>7.4</v>
       </c>
       <c r="M21" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="N21" t="n">
         <v>0.323</v>
       </c>
       <c r="O21" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P21" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R21" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S21" t="n">
         <v>30.8</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U21" t="n">
         <v>19.7</v>
@@ -4191,25 +4258,25 @@
         <v>22.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>15</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4224,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
         <v>26</v>
@@ -4239,10 +4306,10 @@
         <v>20</v>
       </c>
       <c r="AR21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS21" t="n">
         <v>15</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>16</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4269,10 +4336,10 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>10</v>
@@ -4403,7 +4470,7 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM22" t="n">
         <v>12</v>
@@ -4445,10 +4512,10 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.583</v>
+        <v>0.576</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4510,7 +4577,7 @@
         <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.378</v>
@@ -4519,34 +4586,34 @@
         <v>15.3</v>
       </c>
       <c r="P23" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.656</v>
+        <v>0.654</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S23" t="n">
         <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z23" t="n">
         <v>17.5</v>
@@ -4555,25 +4622,25 @@
         <v>20.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF23" t="n">
         <v>10</v>
       </c>
-      <c r="AE23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8</v>
-      </c>
       <c r="AG23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>28</v>
@@ -4582,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4609,13 +4676,13 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
         <v>26</v>
@@ -4636,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
         <v>11</v>
@@ -4791,7 +4858,7 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4800,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
@@ -4943,7 +5010,7 @@
         <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4955,7 +5022,7 @@
         <v>14</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
         <v>18</v>
@@ -4964,22 +5031,22 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.459</v>
+        <v>0.467</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,31 +5114,31 @@
         <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L26" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.35</v>
+        <v>0.346</v>
       </c>
       <c r="O26" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S26" t="n">
         <v>29.8</v>
@@ -5086,7 +5153,7 @@
         <v>14.1</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
         <v>5</v>
@@ -5095,19 +5162,19 @@
         <v>4.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,28 +5186,28 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM26" t="n">
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5149,10 +5216,10 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5164,7 +5231,7 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>16</v>
@@ -5176,13 +5243,13 @@
         <v>10</v>
       </c>
       <c r="BA26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB26" t="n">
         <v>14</v>
       </c>
-      <c r="BB26" t="n">
-        <v>13</v>
-      </c>
       <c r="BC26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
         <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.328</v>
+        <v>0.317</v>
       </c>
       <c r="H27" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
@@ -5241,13 +5308,13 @@
         <v>20.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.316</v>
+        <v>0.315</v>
       </c>
       <c r="O27" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P27" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.738</v>
@@ -5256,16 +5323,16 @@
         <v>13.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U27" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V27" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
         <v>8.5</v>
@@ -5277,22 +5344,22 @@
         <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.1</v>
+        <v>-6.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
         <v>27</v>
@@ -5334,31 +5401,31 @@
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.361</v>
+        <v>0.35</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J29" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L29" t="n">
         <v>5.6</v>
@@ -5611,13 +5678,13 @@
         <v>16.8</v>
       </c>
       <c r="P29" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S29" t="n">
         <v>31.2</v>
@@ -5626,7 +5693,7 @@
         <v>41.7</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
         <v>15</v>
@@ -5638,43 +5705,43 @@
         <v>4.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
         <v>23.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ29" t="n">
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>20</v>
@@ -5692,7 +5759,7 @@
         <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -5892,13 +5959,13 @@
         <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6062,7 +6129,7 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-15-2011-12</t>
+          <t>2012-04-15</t>
         </is>
       </c>
     </row>
